--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T01:44:04+00:00</t>
+    <t>2026-01-03T21:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-03T21:32:36+00:00</t>
+    <t>2026-01-26T10:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T10:54:48+00:00</t>
+    <t>2026-01-26T11:35:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>90</v>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T11:35:16+00:00</t>
+    <t>2026-01-26T23:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -673,8 +673,9 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://opennursingcoreig.com/CodeSystem/onc-observation-codes"/&gt;
-    &lt;code value="swallowing"/&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="30175009"/&gt;
+    &lt;display value="Initial oral examination"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-26T23:55:12+00:00</t>
+    <t>2026-01-27T00:24:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T00:24:44+00:00</t>
+    <t>2026-01-27T01:09:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T01:09:05+00:00</t>
+    <t>2026-01-27T08:26:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T08:26:02+00:00</t>
+    <t>2026-01-27T09:30:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T09:30:37+00:00</t>
+    <t>2026-06-29T21:13:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T21:13:26+00:00</t>
+    <t>2026-07-04T08:39:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T08:39:09+00:00</t>
+    <t>2026-07-04T09:17:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-04T09:17:49+00:00</t>
+    <t>2026-07-09T21:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:51:52+00:00</t>
+    <t>2026-07-09T22:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:02:23+00:00</t>
+    <t>2026-07-09T22:05:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:05:12+00:00</t>
+    <t>2026-07-09T22:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T22:28:17+00:00</t>
+    <t>2026-07-10T11:01:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T11:01:35+00:00</t>
+    <t>2026-07-11T09:35:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:35:24+00:00</t>
+    <t>2026-07-11T09:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T09:46:48+00:00</t>
+    <t>2026-07-11T14:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:02:42+00:00</t>
+    <t>2026-07-11T14:17:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:17:07+00:00</t>
+    <t>2026-07-11T14:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:32:04+00:00</t>
+    <t>2026-07-11T14:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-onc-swallowing-assessment.xlsx
+++ b/StructureDefinition-onc-swallowing-assessment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-11T14:47:20+00:00</t>
+    <t>2026-07-11T18:02:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
